--- a/Fixed.xlsx
+++ b/Fixed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Myapp\Spend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CDFEF8-F5AF-43CF-A9D7-0737685D1497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E593742-305F-461B-B3CE-5E2A71A79E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14580" yWindow="2470" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30110" yWindow="2650" windowWidth="28800" windowHeight="14940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,6 @@
     <t>Electric</t>
   </si>
   <si>
-    <t>Car</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
     <t>Wifi</t>
   </si>
   <si>
@@ -85,6 +79,12 @@
   </si>
   <si>
     <t>Amount</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Car Insurance</t>
   </si>
 </sst>
 </file>
@@ -411,13 +411,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>17</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -447,7 +447,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -458,7 +458,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>33</v>
@@ -466,10 +466,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>237</v>
@@ -477,10 +477,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>33</v>
@@ -488,10 +488,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -499,10 +499,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
         <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -510,10 +510,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -521,10 +521,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>7.5</v>
@@ -532,10 +532,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>8.25</v>
@@ -543,10 +543,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
         <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
       </c>
       <c r="C13">
         <v>8</v>
@@ -554,10 +554,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>22.5</v>

--- a/Fixed.xlsx
+++ b/Fixed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Myapp\Spend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E593742-305F-461B-B3CE-5E2A71A79E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE560B9-5C39-4DBB-AD3E-CE7C66320B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30110" yWindow="2650" windowWidth="28800" windowHeight="14940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -439,7 +439,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -450,7 +450,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -461,7 +461,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -472,7 +472,7 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>237</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
